--- a/jira_export_2026-09-25.xlsx
+++ b/jira_export_2026-09-25.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>49,437 €</t>
+          <t>50,426 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -779,7 +779,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>36,575 €</t>
+          <t>37,564 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>409 h</t>
+          <t>415 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -945,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P182"/>
+  <dimension ref="A1:P183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -3542,13 +3542,13 @@
         </is>
       </c>
       <c r="N39" s="13" t="n">
-        <v>1505</v>
-      </c>
-      <c r="O39" s="17" t="n">
-        <v>0</v>
+        <v>657.9</v>
+      </c>
+      <c r="O39" s="13" t="n">
+        <v>989</v>
       </c>
       <c r="P39" s="13" t="n">
-        <v>0</v>
+        <v>329.67</v>
       </c>
     </row>
     <row r="40">
@@ -9551,7 +9551,7 @@
         <v>10</v>
       </c>
       <c r="K123" s="12" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>10</v>
       </c>
       <c r="K124" s="15" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="L124" s="15" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
         <v>10</v>
       </c>
       <c r="K125" s="12" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="L125" s="12" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>10</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="L126" s="15" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>10</v>
       </c>
       <c r="K127" s="12" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="L127" s="12" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>21</v>
       </c>
       <c r="K156" s="15" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="L156" s="15" t="inlineStr"/>
       <c r="M156" s="15" t="inlineStr"/>
@@ -12322,12 +12322,12 @@
     <row r="164">
       <c r="A164" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C164" s="15" t="inlineStr">
@@ -12337,7 +12337,7 @@
       </c>
       <c r="D164" s="15" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E164" s="15" t="n">
@@ -12360,11 +12360,11 @@
       </c>
       <c r="I164" s="15" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J164" s="15" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K164" s="15" t="n">
         <v>0.5</v>
@@ -12384,22 +12384,22 @@
     <row r="165">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B165" s="12" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E165" s="12" t="n">
@@ -12422,14 +12422,14 @@
       </c>
       <c r="I165" s="12" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J165" s="12" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="K165" s="12" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L165" s="12" t="inlineStr"/>
       <c r="M165" s="12" t="inlineStr"/>
@@ -12446,12 +12446,12 @@
     <row r="166">
       <c r="A166" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C166" s="15" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="D166" s="15" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E166" s="15" t="n">
@@ -12479,19 +12479,19 @@
       </c>
       <c r="H166" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I166" s="15" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J166" s="15" t="n">
         <v>34</v>
       </c>
       <c r="K166" s="15" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L166" s="15" t="inlineStr"/>
       <c r="M166" s="15" t="inlineStr"/>
@@ -12508,22 +12508,22 @@
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B167" s="12" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E167" s="12" t="n">
@@ -12546,14 +12546,14 @@
       </c>
       <c r="I167" s="12" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J167" s="12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K167" s="12" t="n">
-        <v>3.58</v>
+        <v>1</v>
       </c>
       <c r="L167" s="12" t="inlineStr"/>
       <c r="M167" s="12" t="inlineStr"/>
@@ -12570,22 +12570,22 @@
     <row r="168">
       <c r="A168" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13128</t>
         </is>
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
         </is>
       </c>
       <c r="C168" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D168" s="15" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E168" s="15" t="n">
@@ -12598,35 +12598,27 @@
       </c>
       <c r="G168" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H168" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I168" s="15" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>30/10/2023</t>
         </is>
       </c>
       <c r="J168" s="15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K168" s="15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L168" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M168" s="15" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>3.58</v>
+      </c>
+      <c r="L168" s="15" t="inlineStr"/>
+      <c r="M168" s="15" t="inlineStr"/>
       <c r="N168" s="16" t="n">
         <v>0</v>
       </c>
@@ -12640,22 +12632,22 @@
     <row r="169">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B169" s="12" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E169" s="12" t="n">
@@ -12668,23 +12660,35 @@
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H169" s="12" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H169" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I169" s="12" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J169" s="12" t="n">
         <v>36</v>
       </c>
       <c r="K169" s="12" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L169" s="12" t="inlineStr"/>
-      <c r="M169" s="12" t="inlineStr"/>
+        <v>2.25</v>
+      </c>
+      <c r="L169" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M169" s="12" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N169" s="13" t="n">
         <v>0</v>
       </c>
@@ -12698,12 +12702,12 @@
     <row r="170">
       <c r="A170" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C170" s="15" t="inlineStr">
@@ -12713,7 +12717,7 @@
       </c>
       <c r="D170" s="15" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E170" s="15" t="n">
@@ -12729,32 +12733,20 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H170" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H170" s="15" t="inlineStr"/>
       <c r="I170" s="15" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J170" s="15" t="n">
         <v>36</v>
       </c>
       <c r="K170" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L170" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M170" s="15" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L170" s="15" t="inlineStr"/>
+      <c r="M170" s="15" t="inlineStr"/>
       <c r="N170" s="16" t="n">
         <v>0</v>
       </c>
@@ -12768,28 +12760,26 @@
     <row r="171">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B171" s="12" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E171" s="12" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E171" s="12" t="n">
+        <v/>
       </c>
       <c r="F171" s="12" t="inlineStr">
         <is>
@@ -12803,22 +12793,30 @@
       </c>
       <c r="H171" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I171" s="12" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J171" s="12" t="n">
         <v>36</v>
       </c>
       <c r="K171" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L171" s="12" t="inlineStr"/>
-      <c r="M171" s="12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L171" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M171" s="12" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N171" s="13" t="n">
         <v>0</v>
       </c>
@@ -12832,23 +12830,27 @@
     <row r="172">
       <c r="A172" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C172" s="15" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C172" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D172" s="15" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E172" s="15" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F172" s="15" t="inlineStr">
@@ -12863,19 +12865,19 @@
       </c>
       <c r="H172" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I172" s="15" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J172" s="15" t="n">
         <v>36</v>
       </c>
       <c r="K172" s="15" t="n">
-        <v>5.25</v>
+        <v>0.25</v>
       </c>
       <c r="L172" s="15" t="inlineStr"/>
       <c r="M172" s="15" t="inlineStr"/>
@@ -12892,21 +12894,25 @@
     <row r="173">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B173" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C173" s="12" t="inlineStr"/>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
-        </is>
-      </c>
-      <c r="E173" s="12" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E173" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F173" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -12914,52 +12920,52 @@
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H173" s="12" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H173" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I173" s="12" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J173" s="12" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="K173" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L173" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="L173" s="12" t="inlineStr"/>
       <c r="M173" s="12" t="inlineStr"/>
       <c r="N173" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O173" s="13" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P173" s="13" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="14" t="inlineStr">
         <is>
-          <t>PSC-1334</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MOUY</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C174" s="15" t="inlineStr"/>
       <c r="D174" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MOUY</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="E174" s="15" t="inlineStr"/>
@@ -12970,7 +12976,7 @@
       </c>
       <c r="G174" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H174" s="15" t="inlineStr"/>
@@ -12983,35 +12989,39 @@
         <v>2</v>
       </c>
       <c r="K174" s="15" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L174" s="15" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L174" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
       <c r="M174" s="15" t="inlineStr"/>
       <c r="N174" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O174" s="16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P174" s="16" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>PSC-1326</t>
+          <t>PSC-1334</t>
         </is>
       </c>
       <c r="B175" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>MAIRIE DE MOUY</t>
         </is>
       </c>
       <c r="C175" s="12" t="inlineStr"/>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>MAIRIE DE MOUY</t>
         </is>
       </c>
       <c r="E175" s="12" t="inlineStr"/>
@@ -13028,14 +13038,14 @@
       <c r="H175" s="12" t="inlineStr"/>
       <c r="I175" s="12" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J175" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K175" s="12" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="L175" s="12" t="inlineStr"/>
       <c r="M175" s="12" t="inlineStr"/>
@@ -13052,18 +13062,18 @@
     <row r="176">
       <c r="A176" s="14" t="inlineStr">
         <is>
-          <t>PSC-1315</t>
+          <t>PSC-1326</t>
         </is>
       </c>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="C176" s="15" t="inlineStr"/>
       <c r="D176" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E176" s="15" t="inlineStr"/>
@@ -13074,31 +13084,23 @@
       </c>
       <c r="G176" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H176" s="15" t="inlineStr"/>
       <c r="I176" s="15" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J176" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K176" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L176" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34778</t>
-        </is>
-      </c>
-      <c r="M176" s="15" t="inlineStr">
-        <is>
-          <t>00172868</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L176" s="15" t="inlineStr"/>
+      <c r="M176" s="15" t="inlineStr"/>
       <c r="N176" s="16" t="n">
         <v>0</v>
       </c>
@@ -13112,18 +13114,18 @@
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>PSC-1300</t>
+          <t>PSC-1315</t>
         </is>
       </c>
       <c r="B177" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr"/>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="E177" s="12" t="inlineStr"/>
@@ -13134,23 +13136,31 @@
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H177" s="12" t="inlineStr"/>
       <c r="I177" s="12" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="J177" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K177" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L177" s="12" t="inlineStr"/>
-      <c r="M177" s="12" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L177" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-34778</t>
+        </is>
+      </c>
+      <c r="M177" s="12" t="inlineStr">
+        <is>
+          <t>00172868</t>
+        </is>
+      </c>
       <c r="N177" s="13" t="n">
         <v>0</v>
       </c>
@@ -13164,18 +13174,18 @@
     <row r="178">
       <c r="A178" s="14" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1300</t>
         </is>
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="C178" s="15" t="inlineStr"/>
       <c r="D178" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="E178" s="15" t="inlineStr"/>
@@ -13186,31 +13196,23 @@
       </c>
       <c r="G178" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H178" s="15" t="inlineStr"/>
       <c r="I178" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J178" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K178" s="15" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="L178" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M178" s="15" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L178" s="15" t="inlineStr"/>
+      <c r="M178" s="15" t="inlineStr"/>
       <c r="N178" s="16" t="n">
         <v>0</v>
       </c>
@@ -13224,18 +13226,18 @@
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>PSC-1158</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B179" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE PLERIN</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr"/>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE PLERIN</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E179" s="12" t="inlineStr"/>
@@ -13246,23 +13248,31 @@
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H179" s="12" t="inlineStr"/>
       <c r="I179" s="12" t="inlineStr">
         <is>
-          <t>25/02/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J179" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K179" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L179" s="12" t="inlineStr"/>
-      <c r="M179" s="12" t="inlineStr"/>
+        <v>4.25</v>
+      </c>
+      <c r="L179" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M179" s="12" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N179" s="13" t="n">
         <v>0</v>
       </c>
@@ -13276,18 +13286,18 @@
     <row r="180">
       <c r="A180" s="14" t="inlineStr">
         <is>
-          <t>PSC-850</t>
+          <t>PSC-1158</t>
         </is>
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>COMMUNE DE PLERIN</t>
         </is>
       </c>
       <c r="C180" s="15" t="inlineStr"/>
       <c r="D180" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>COMMUNE DE PLERIN</t>
         </is>
       </c>
       <c r="E180" s="15" t="inlineStr"/>
@@ -13304,14 +13314,14 @@
       <c r="H180" s="15" t="inlineStr"/>
       <c r="I180" s="15" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>25/02/2026</t>
         </is>
       </c>
       <c r="J180" s="15" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K180" s="15" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="L180" s="15" t="inlineStr"/>
       <c r="M180" s="15" t="inlineStr"/>
@@ -13328,18 +13338,18 @@
     <row r="181">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>PSC-668</t>
+          <t>PSC-850</t>
         </is>
       </c>
       <c r="B181" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE DUGNY</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="C181" s="12" t="inlineStr"/>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE DUGNY</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="E181" s="12" t="inlineStr"/>
@@ -13356,11 +13366,11 @@
       <c r="H181" s="12" t="inlineStr"/>
       <c r="I181" s="12" t="inlineStr">
         <is>
-          <t>04/04/2025</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="J181" s="12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K181" s="12" t="n">
         <v>0.25</v>
@@ -13378,31 +13388,83 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="18" t="inlineStr">
+      <c r="A182" s="14" t="inlineStr">
+        <is>
+          <t>PSC-668</t>
+        </is>
+      </c>
+      <c r="B182" s="15" t="inlineStr">
+        <is>
+          <t>VILLE DE DUGNY</t>
+        </is>
+      </c>
+      <c r="C182" s="15" t="inlineStr"/>
+      <c r="D182" s="15" t="inlineStr">
+        <is>
+          <t>VILLE DE DUGNY</t>
+        </is>
+      </c>
+      <c r="E182" s="15" t="inlineStr"/>
+      <c r="F182" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G182" s="15" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H182" s="15" t="inlineStr"/>
+      <c r="I182" s="15" t="inlineStr">
+        <is>
+          <t>04/04/2025</t>
+        </is>
+      </c>
+      <c r="J182" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="K182" s="15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L182" s="15" t="inlineStr"/>
+      <c r="M182" s="15" t="inlineStr"/>
+      <c r="N182" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O182" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B182" s="18" t="inlineStr"/>
-      <c r="C182" s="18" t="inlineStr"/>
-      <c r="D182" s="18" t="inlineStr"/>
-      <c r="E182" s="18" t="inlineStr"/>
-      <c r="F182" s="18" t="inlineStr"/>
-      <c r="G182" s="18" t="inlineStr"/>
-      <c r="H182" s="18" t="inlineStr"/>
-      <c r="I182" s="18" t="inlineStr"/>
-      <c r="J182" s="18" t="inlineStr"/>
-      <c r="K182" s="18" t="inlineStr"/>
-      <c r="L182" s="18" t="inlineStr"/>
-      <c r="M182" s="18" t="inlineStr"/>
-      <c r="N182" s="19" t="n">
-        <v>49032.67600000001</v>
-      </c>
-      <c r="O182" s="19" t="n">
-        <v>49437.358</v>
-      </c>
-      <c r="P182" s="19" t="n">
-        <v>181.7</v>
+      <c r="B183" s="18" t="inlineStr"/>
+      <c r="C183" s="18" t="inlineStr"/>
+      <c r="D183" s="18" t="inlineStr"/>
+      <c r="E183" s="18" t="inlineStr"/>
+      <c r="F183" s="18" t="inlineStr"/>
+      <c r="G183" s="18" t="inlineStr"/>
+      <c r="H183" s="18" t="inlineStr"/>
+      <c r="I183" s="18" t="inlineStr"/>
+      <c r="J183" s="18" t="inlineStr"/>
+      <c r="K183" s="18" t="inlineStr"/>
+      <c r="L183" s="18" t="inlineStr"/>
+      <c r="M183" s="18" t="inlineStr"/>
+      <c r="N183" s="19" t="n">
+        <v>48185.576</v>
+      </c>
+      <c r="O183" s="19" t="n">
+        <v>50426.358</v>
+      </c>
+      <c r="P183" s="19" t="n">
+        <v>182.32</v>
       </c>
     </row>
   </sheetData>
@@ -13585,6 +13647,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A179" r:id="rId175"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A180" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A181" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A182" r:id="rId178"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14828,16 +14891,16 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>139.67</v>
+        <v>141.42</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>44.92</v>
+        <v>47.67</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>19.25</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>203.83</v>
+        <v>208.33</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>30.67</v>
@@ -14847,7 +14910,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>48.7%</t>
         </is>
       </c>
     </row>
@@ -14889,7 +14952,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>96</v>
+        <v>97.75</v>
       </c>
     </row>
   </sheetData>
@@ -14974,10 +15037,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>403159</v>
+        <v>402170</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>174475</v>
+        <v>173486</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>228683</v>
@@ -15024,10 +15087,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>225166</v>
+        <v>224177</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>122346</v>
+        <v>121357</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>102820</v>
